--- a/education_forms/030_child_play_activity_assessment--education_forms.xlsx
+++ b/education_forms/030_child_play_activity_assessment--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,8 +939,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,12 +968,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'solitary_play',_'value':_'solitary'}</t>
+          <t>solitary_play</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Solitary Play', 'value': 'solitary'}</t>
+          <t>Solitary Play</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'parallel_play',_'value':_'parallel'}</t>
+          <t>parallel_play</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Parallel Play', 'value': 'parallel'}</t>
+          <t>Parallel Play</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'associative_play',_'value':_'associative'}</t>
+          <t>associative_play</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Associative Play', 'value': 'associative'}</t>
+          <t>Associative Play</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cooperative_play',_'value':_'cooperative'}</t>
+          <t>cooperative_play</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Cooperative Play', 'value': 'cooperative'}</t>
+          <t>Cooperative Play</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'high_engagement',_'value':_'high'}</t>
+          <t>high_engagement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'High Engagement', 'value': 'high'}</t>
+          <t>High Engagement</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moderate_engagement',_'value':_'moderate'}</t>
+          <t>moderate_engagement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate Engagement', 'value': 'moderate'}</t>
+          <t>Moderate Engagement</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low_engagement',_'value':_'low'}</t>
+          <t>low_engagement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low Engagement', 'value': 'low'}</t>
+          <t>Low Engagement</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'disinterested_or_detached',_'value':_'none'}</t>
+          <t>disinterested_or_detached</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Disinterested or Detached', 'value': 'none'}</t>
+          <t>Disinterested or Detached</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'always_demonstrates',_'value':_'always'}</t>
+          <t>always_demonstrates</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Always Demonstrates', 'value': 'always'}</t>
+          <t>Always Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_demonstrates',_'value':_'sometimes'}</t>
+          <t>sometimes_demonstrates</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes Demonstrates', 'value': 'sometimes'}</t>
+          <t>Sometimes Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_demonstrates',_'value':_'rarely'}</t>
+          <t>rarely_demonstrates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely Demonstrates', 'value': 'rarely'}</t>
+          <t>Rarely Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'frequent_and_clear',_'value':_'frequent'}</t>
+          <t>frequent_and_clear</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Frequent and Clear', 'value': 'frequent'}</t>
+          <t>Frequent and Clear</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'occasional_communication',_'value':_'occasional'}</t>
+          <t>occasional_communication</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Occasional Communication', 'value': 'occasional'}</t>
+          <t>Occasional Communication</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'minimal_or_non-verbal',_'value':_'minimal'}</t>
+          <t>minimal_or_non-verbal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Minimal or Non-verbal', 'value': 'minimal'}</t>
+          <t>Minimal or Non-verbal</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'fine_motor_control',_'value':_'fine_motor'}</t>
+          <t>fine_motor_control</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Fine Motor Control', 'value': 'fine_motor'}</t>
+          <t>Fine Motor Control</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'problem_solving_and_logic',_'value':_'logic'}</t>
+          <t>problem_solving_and_logic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Problem Solving and Logic', 'value': 'logic'}</t>
+          <t>Problem Solving and Logic</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'imagination_and_roleplay',_'value':_'imagination'}</t>
+          <t>imagination_and_roleplay</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Imagination and Roleplay', 'value': 'imagination'}</t>
+          <t>Imagination and Roleplay</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'empathy_and_caring',_'value':_'empathy'}</t>
+          <t>empathy_and_caring</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Empathy and Caring', 'value': 'empathy'}</t>
+          <t>Empathy and Caring</t>
         </is>
       </c>
     </row>
